--- a/data/trans_dic/P16A07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,78</t>
+          <t>1,01; 4,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,72</t>
+          <t>2,03; 6,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,39</t>
+          <t>1,31; 5,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,44</t>
+          <t>0,54; 3,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 12,09</t>
+          <t>5,1; 12,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 11,78</t>
+          <t>4,88; 11,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 12,29</t>
+          <t>5,56; 12,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,53</t>
+          <t>3,13; 6,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,31</t>
+          <t>3,49; 7,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,86</t>
+          <t>3,84; 7,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,94</t>
+          <t>4,0; 7,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,28</t>
+          <t>2,11; 4,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,83</t>
+          <t>0,2; 1,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,22</t>
+          <t>1,07; 4,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,95</t>
+          <t>0,64; 2,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,12</t>
+          <t>2,15; 6,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,04</t>
+          <t>3,92; 8,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 10,81</t>
+          <t>5,99; 10,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,9</t>
+          <t>4,34; 8,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,1</t>
+          <t>7,93; 12,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,85</t>
+          <t>2,31; 4,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,13</t>
+          <t>4,1; 7,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,5</t>
+          <t>2,85; 5,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,3</t>
+          <t>5,53; 8,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,37</t>
+          <t>0,32; 3,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,9</t>
+          <t>2,17; 7,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,17</t>
+          <t>3,37; 8,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,32</t>
+          <t>2,63; 7,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 12,52</t>
+          <t>5,88; 12,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,19</t>
+          <t>2,36; 6,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,32</t>
+          <t>7,38; 12,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,6</t>
+          <t>1,71; 4,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 9,04</t>
+          <t>4,8; 8,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,99</t>
+          <t>1,44; 4,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,36</t>
+          <t>6,14; 9,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,17</t>
+          <t>0,24; 2,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,08</t>
+          <t>0,55; 2,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,69</t>
+          <t>0,79; 3,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,48</t>
+          <t>2,66; 8,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,84</t>
+          <t>2,77; 7,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 13,42</t>
+          <t>7,56; 13,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,2</t>
+          <t>4,61; 10,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,46</t>
+          <t>2,5; 6,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,97</t>
+          <t>1,71; 4,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,66</t>
+          <t>4,36; 7,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,3</t>
+          <t>3,28; 6,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,28</t>
+          <t>2,97; 6,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,96</t>
+          <t>2,18; 7,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,0</t>
+          <t>1,02; 6,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,09</t>
+          <t>3,09; 9,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,23</t>
+          <t>0,31; 3,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 16,58</t>
+          <t>7,47; 17,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,71; 20,71</t>
+          <t>11,1; 20,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 13,78</t>
+          <t>5,7; 13,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,48</t>
+          <t>3,54; 7,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,77</t>
+          <t>5,6; 10,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,52</t>
+          <t>6,49; 12,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,9</t>
+          <t>5,2; 9,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,64</t>
+          <t>2,35; 4,7</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,91</t>
+          <t>1,83; 6,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,08</t>
+          <t>0,3; 2,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,68</t>
+          <t>3,01; 7,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,83</t>
+          <t>1,73; 5,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,66; 12,14</t>
+          <t>5,86; 12,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,68</t>
+          <t>5,79; 12,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,59</t>
+          <t>4,46; 8,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,32</t>
+          <t>1,09; 3,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,43</t>
+          <t>4,58; 8,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,03</t>
+          <t>3,17; 7,15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 7,3</t>
+          <t>4,24; 7,45</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,21</t>
+          <t>1,01; 3,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,2</t>
+          <t>2,84; 6,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,88</t>
+          <t>0,64; 2,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,28</t>
+          <t>3,05; 6,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,05</t>
+          <t>5,65; 9,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,55</t>
+          <t>5,41; 9,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,29</t>
+          <t>3,91; 7,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,04</t>
+          <t>3,38; 10,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,07</t>
+          <t>3,7; 6,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,29</t>
+          <t>4,66; 7,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,56</t>
+          <t>2,44; 4,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,52</t>
+          <t>3,84; 7,6</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,86</t>
+          <t>2,64; 5,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,24</t>
+          <t>1,5; 4,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,9</t>
+          <t>2,17; 4,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,23</t>
+          <t>0,57; 2,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,36; 9,18</t>
+          <t>5,38; 9,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,37</t>
+          <t>4,99; 8,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,87</t>
+          <t>6,76; 10,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,61</t>
+          <t>6,41; 9,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,94</t>
+          <t>4,34; 6,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,0</t>
+          <t>3,59; 5,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,35</t>
+          <t>4,9; 7,56</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,37</t>
+          <t>2,5; 5,29</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,62</t>
+          <t>1,68; 2,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,91</t>
+          <t>2,53; 3,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,69</t>
+          <t>1,73; 2,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,92</t>
+          <t>2,47; 3,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,3</t>
+          <t>5,65; 7,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,26</t>
+          <t>7,46; 9,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,0</t>
+          <t>6,23; 8,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,76; 7,97</t>
+          <t>5,85; 8,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,84; 4,81</t>
+          <t>3,89; 4,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,44</t>
+          <t>5,23; 6,44</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,19; 5,23</t>
+          <t>4,24; 5,27</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,82</t>
+          <t>4,55; 5,8</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2738; 13053</t>
+          <t>2762; 13131</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5733; 19499</t>
+          <t>5900; 19509</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3775; 15830</t>
+          <t>3846; 16978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1670; 10714</t>
+          <t>1671; 9871</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13550; 31527</t>
+          <t>13314; 32392</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13399; 33219</t>
+          <t>13775; 31557</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16558; 35490</t>
+          <t>16047; 34962</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8957; 18909</t>
+          <t>9063; 19196</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18706; 39012</t>
+          <t>18652; 39962</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22328; 44960</t>
+          <t>21979; 44136</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22659; 46262</t>
+          <t>23315; 46191</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12440; 25711</t>
+          <t>12681; 25235</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>995; 9029</t>
+          <t>983; 8889</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6147; 26342</t>
+          <t>5399; 24630</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3158; 14818</t>
+          <t>3194; 14652</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11385; 31687</t>
+          <t>11109; 31460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19728; 40519</t>
+          <t>19732; 41042</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31016; 56506</t>
+          <t>31313; 56830</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23325; 46554</t>
+          <t>22682; 46347</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39166; 62174</t>
+          <t>40757; 64745</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24130; 48382</t>
+          <t>23017; 45555</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40219; 73259</t>
+          <t>42145; 73071</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29589; 56444</t>
+          <t>29217; 55952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56718; 85567</t>
+          <t>57036; 85595</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1019; 10750</t>
+          <t>1024; 12326</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6899; 22311</t>
+          <t>7004; 22902</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6875</t>
+          <t>0; 8508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10638; 25796</t>
+          <t>10638; 25308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8937; 24538</t>
+          <t>8837; 23799</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21389; 42694</t>
+          <t>20039; 42193</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7880; 24191</t>
+          <t>7944; 23190</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25309; 43013</t>
+          <t>25752; 43430</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11916; 30098</t>
+          <t>11196; 29266</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32741; 60046</t>
+          <t>31901; 57701</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9614; 26145</t>
+          <t>9400; 26661</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40086; 62189</t>
+          <t>40836; 63786</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>849; 7766</t>
+          <t>856; 8481</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2036; 11535</t>
+          <t>2042; 10847</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2894; 13664</t>
+          <t>2922; 13575</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7749; 26519</t>
+          <t>8324; 25528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10046; 25407</t>
+          <t>10278; 26131</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29517; 52056</t>
+          <t>29348; 52799</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18304; 39506</t>
+          <t>17848; 38810</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11483; 30722</t>
+          <t>11890; 29601</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12435; 28958</t>
+          <t>12513; 29254</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32958; 58340</t>
+          <t>33220; 59979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24124; 47714</t>
+          <t>24836; 47289</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23670; 49507</t>
+          <t>23413; 50187</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4547; 16178</t>
+          <t>4432; 15012</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2175; 12758</t>
+          <t>2179; 13916</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6015; 19207</t>
+          <t>6519; 19294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>675; 5767</t>
+          <t>546; 5393</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15422; 34433</t>
+          <t>15522; 35517</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23522; 45474</t>
+          <t>24385; 45613</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12714; 30130</t>
+          <t>12459; 29609</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7581; 15603</t>
+          <t>7395; 15311</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23444; 44257</t>
+          <t>23008; 44330</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29016; 54114</t>
+          <t>28030; 54145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22023; 42530</t>
+          <t>22332; 42826</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8903; 17978</t>
+          <t>9090; 18222</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6650</t>
+          <t>0; 7184</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5155; 18943</t>
+          <t>5018; 17760</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>794; 8103</t>
+          <t>797; 7611</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8251; 20701</t>
+          <t>8116; 20959</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4082; 16213</t>
+          <t>4801; 16439</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15787; 33883</t>
+          <t>16346; 35327</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14972; 34623</t>
+          <t>15803; 34556</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11356; 22069</t>
+          <t>11470; 22552</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5995; 18245</t>
+          <t>5992; 19771</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24187; 46655</t>
+          <t>25334; 48230</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17558; 37722</t>
+          <t>16999; 38314</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21655; 38448</t>
+          <t>22310; 39257</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6396; 19765</t>
+          <t>6237; 19497</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18595; 41124</t>
+          <t>18797; 42083</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4319; 18908</t>
+          <t>4190; 18558</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18689; 39209</t>
+          <t>19015; 38531</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35780; 64119</t>
+          <t>36091; 61675</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38105; 66177</t>
+          <t>37476; 65578</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24856; 50371</t>
+          <t>26996; 53757</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30955; 85283</t>
+          <t>28738; 86392</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46760; 76124</t>
+          <t>46409; 75460</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63215; 98802</t>
+          <t>63140; 100962</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32744; 61426</t>
+          <t>32820; 63046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55893; 110825</t>
+          <t>56610; 112016</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20346; 43534</t>
+          <t>19612; 41821</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12783; 32960</t>
+          <t>11691; 33180</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17369; 38135</t>
+          <t>16866; 37932</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4307; 20756</t>
+          <t>5261; 23092</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>42018; 71955</t>
+          <t>42147; 71657</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41374; 68764</t>
+          <t>41003; 72133</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55782; 89837</t>
+          <t>55842; 90263</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>45893; 68664</t>
+          <t>45835; 69000</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>67403; 105862</t>
+          <t>66197; 105297</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>59379; 95867</t>
+          <t>57341; 92989</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>78821; 117912</t>
+          <t>78593; 121342</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>43069; 88311</t>
+          <t>41163; 86952</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>55089; 85755</t>
+          <t>55132; 88484</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>86572; 133555</t>
+          <t>86537; 132995</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57849; 91412</t>
+          <t>58629; 92928</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84745; 135474</t>
+          <t>85505; 134337</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>190280; 246748</t>
+          <t>190996; 247695</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>262752; 328478</t>
+          <t>264554; 331394</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>223043; 283410</t>
+          <t>220920; 288598</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>210501; 291456</t>
+          <t>214142; 293572</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>255230; 320257</t>
+          <t>259067; 319516</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>367529; 448340</t>
+          <t>364473; 448511</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>290464; 362774</t>
+          <t>294186; 365908</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>322144; 414280</t>
+          <t>323773; 413007</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,81</t>
+          <t>1,04; 4,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,72</t>
+          <t>2,03; 6,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,78</t>
+          <t>1,36; 5,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,17</t>
+          <t>0,51; 3,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 12,42</t>
+          <t>5,09; 11,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,19</t>
+          <t>4,65; 11,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,11</t>
+          <t>5,71; 12,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,63</t>
+          <t>3,08; 6,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,49</t>
+          <t>3,58; 7,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,71</t>
+          <t>3,83; 7,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,93</t>
+          <t>4,01; 7,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,2</t>
+          <t>2,11; 4,18</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,8</t>
+          <t>0,22; 2,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,88</t>
+          <t>1,02; 4,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,92</t>
+          <t>0,64; 2,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,08</t>
+          <t>2,29; 5,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,14</t>
+          <t>4,06; 8,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,87</t>
+          <t>6,02; 11,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,86</t>
+          <t>4,51; 9,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,6</t>
+          <t>7,65; 12,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,57</t>
+          <t>2,43; 4,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 7,11</t>
+          <t>4,06; 7,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,46</t>
+          <t>2,86; 5,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,3</t>
+          <t>5,34; 8,2</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,87</t>
+          <t>0,32; 3,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,09</t>
+          <t>2,2; 7,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,02</t>
+          <t>3,81; 8,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,1</t>
+          <t>2,66; 7,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,37</t>
+          <t>6,0; 12,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,9</t>
+          <t>2,25; 6,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 12,44</t>
+          <t>7,5; 12,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,47</t>
+          <t>1,76; 4,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,69</t>
+          <t>4,48; 8,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,07</t>
+          <t>1,43; 4,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 9,6</t>
+          <t>6,25; 9,58</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,36</t>
+          <t>0,24; 2,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,9</t>
+          <t>0,54; 3,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,67</t>
+          <t>0,78; 3,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,17</t>
+          <t>2,29; 7,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,03</t>
+          <t>2,7; 6,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,61</t>
+          <t>7,35; 13,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,02</t>
+          <t>4,75; 10,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,23</t>
+          <t>3,88; 7,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,01</t>
+          <t>1,64; 4,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,87</t>
+          <t>4,22; 7,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,24</t>
+          <t>3,37; 6,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,37</t>
+          <t>3,5; 6,63</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,38</t>
+          <t>2,24; 7,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,55</t>
+          <t>1,26; 5,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,13</t>
+          <t>2,86; 9,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,02</t>
+          <t>0,28; 2,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 17,1</t>
+          <t>7,79; 16,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,1; 20,77</t>
+          <t>10,79; 20,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 13,55</t>
+          <t>5,86; 13,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,34</t>
+          <t>3,36; 7,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,79</t>
+          <t>5,53; 10,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,53</t>
+          <t>6,66; 12,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,96</t>
+          <t>5,09; 9,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,7</t>
+          <t>2,24; 4,42</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,48</t>
+          <t>1,87; 6,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,89</t>
+          <t>0,3; 2,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,77</t>
+          <t>3,0; 7,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,91</t>
+          <t>1,51; 6,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,66</t>
+          <t>5,77; 12,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 12,65</t>
+          <t>5,37; 12,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,77</t>
+          <t>4,26; 8,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,6</t>
+          <t>1,08; 3,3</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,72</t>
+          <t>4,47; 8,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,15</t>
+          <t>3,19; 6,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,45</t>
+          <t>4,15; 7,06</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,17</t>
+          <t>1,07; 3,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,35</t>
+          <t>2,79; 6,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,83</t>
+          <t>0,67; 2,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,17</t>
+          <t>3,14; 6,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,66</t>
+          <t>5,42; 9,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,47</t>
+          <t>5,49; 9,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,78</t>
+          <t>3,76; 7,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,17</t>
+          <t>7,53; 11,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,02</t>
+          <t>3,7; 6,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,45</t>
+          <t>4,54; 7,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,68</t>
+          <t>2,57; 4,69</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,6</t>
+          <t>5,71; 8,33</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,63</t>
+          <t>2,75; 5,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,27</t>
+          <t>1,64; 4,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,87</t>
+          <t>2,24; 4,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,49</t>
+          <t>1,2; 3,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,15</t>
+          <t>5,35; 9,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,78</t>
+          <t>5,04; 8,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,93</t>
+          <t>6,9; 11,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,41; 9,65</t>
+          <t>6,23; 9,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,9</t>
+          <t>4,43; 6,91</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,82</t>
+          <t>3,62; 5,91</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,9; 7,56</t>
+          <t>4,92; 7,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,29</t>
+          <t>4,08; 5,94</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,7</t>
+          <t>1,68; 2,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,89</t>
+          <t>2,52; 3,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,74</t>
+          <t>1,72; 2,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,88</t>
+          <t>2,85; 4,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,33</t>
+          <t>5,64; 7,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,34</t>
+          <t>7,41; 9,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,14</t>
+          <t>6,29; 8,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,85; 8,03</t>
+          <t>6,95; 8,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,89; 4,8</t>
+          <t>3,86; 4,86</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,44</t>
+          <t>5,21; 6,38</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,27</t>
+          <t>4,25; 5,28</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,8</t>
+          <t>5,17; 6,12</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>18726</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2762; 13131</t>
+          <t>2847; 12451</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5900; 19509</t>
+          <t>5880; 19285</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3846; 16978</t>
+          <t>3983; 15826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1671; 9871</t>
+          <t>1628; 9630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13314; 32392</t>
+          <t>13267; 30909</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13775; 31557</t>
+          <t>13109; 31169</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16047; 34962</t>
+          <t>16498; 35398</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9063; 19196</t>
+          <t>9719; 20596</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18652; 39962</t>
+          <t>19103; 40753</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21979; 44136</t>
+          <t>21912; 44716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23315; 46191</t>
+          <t>23381; 46465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12681; 25235</t>
+          <t>13397; 26564</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50388</t>
+          <t>51877</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69658</t>
+          <t>71546</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>983; 8889</t>
+          <t>1065; 10129</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5399; 24630</t>
+          <t>5125; 23370</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3194; 14652</t>
+          <t>3206; 13927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11109; 31460</t>
+          <t>12109; 31637</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19732; 41042</t>
+          <t>20485; 40954</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31313; 56830</t>
+          <t>31467; 58118</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22682; 46347</t>
+          <t>23614; 47474</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40757; 64745</t>
+          <t>41702; 65609</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23017; 45555</t>
+          <t>24202; 46616</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42145; 73071</t>
+          <t>41701; 73845</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29217; 55952</t>
+          <t>29360; 56654</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57036; 85595</t>
+          <t>57405; 88097</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50495</t>
+          <t>52579</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1024; 12326</t>
+          <t>1026; 10839</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7004; 22902</t>
+          <t>7098; 23254</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8508</t>
+          <t>0; 7615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10638; 25308</t>
+          <t>12005; 27456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8837; 23799</t>
+          <t>8926; 24046</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20039; 42193</t>
+          <t>20473; 43594</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7944; 23190</t>
+          <t>7571; 23378</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25752; 43430</t>
+          <t>26721; 44331</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11196; 29266</t>
+          <t>11495; 29039</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31901; 57701</t>
+          <t>29757; 56939</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9400; 26661</t>
+          <t>9351; 26228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40836; 63786</t>
+          <t>41972; 64363</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>38571</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>856; 8481</t>
+          <t>852; 7698</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2042; 10847</t>
+          <t>2005; 11532</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2922; 13575</t>
+          <t>2878; 13246</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8324; 25528</t>
+          <t>8549; 28379</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10278; 26131</t>
+          <t>10030; 24937</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29348; 52799</t>
+          <t>28517; 51815</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17848; 38810</t>
+          <t>18398; 38904</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11890; 29601</t>
+          <t>16373; 31996</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12513; 29254</t>
+          <t>11992; 29425</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33220; 59979</t>
+          <t>32160; 57946</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24836; 47289</t>
+          <t>25487; 47200</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23413; 50187</t>
+          <t>27817; 52657</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>13641</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4432; 15012</t>
+          <t>4554; 15799</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2179; 13916</t>
+          <t>2680; 12529</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6519; 19294</t>
+          <t>6041; 19283</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546; 5393</t>
+          <t>571; 5847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15522; 35517</t>
+          <t>16178; 34929</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24385; 45613</t>
+          <t>23698; 45133</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12459; 29609</t>
+          <t>12815; 30040</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7395; 15311</t>
+          <t>7629; 16067</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23008; 44330</t>
+          <t>22737; 44925</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28030; 54145</t>
+          <t>28770; 52463</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22332; 42826</t>
+          <t>21860; 42593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9090; 18222</t>
+          <t>9715; 19129</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29596</t>
+          <t>29393</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 7184</t>
+          <t>0; 7195</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5018; 17760</t>
+          <t>5121; 18444</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>797; 7611</t>
+          <t>787; 7760</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8116; 20959</t>
+          <t>8128; 20255</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4801; 16439</t>
+          <t>4200; 17030</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16346; 35327</t>
+          <t>16109; 34503</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15803; 34556</t>
+          <t>14670; 33561</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11470; 22552</t>
+          <t>11223; 22398</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5992; 19771</t>
+          <t>5920; 18098</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25334; 48230</t>
+          <t>24723; 47750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16999; 38314</t>
+          <t>17109; 36703</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22310; 39257</t>
+          <t>22156; 37716</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>32949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>70561</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>103510</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6237; 19497</t>
+          <t>6592; 19409</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18797; 42083</t>
+          <t>18461; 40934</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4190; 18558</t>
+          <t>4409; 19084</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19015; 38531</t>
+          <t>22624; 47514</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>36091; 61675</t>
+          <t>34622; 62072</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37476; 65578</t>
+          <t>37999; 66696</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26996; 53757</t>
+          <t>25998; 52187</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28738; 86392</t>
+          <t>58148; 87230</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46409; 75460</t>
+          <t>46414; 76462</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63140; 100962</t>
+          <t>61576; 101005</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32820; 63046</t>
+          <t>34627; 63149</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56610; 112016</t>
+          <t>85183; 124259</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>56273</t>
+          <t>64572</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69299</t>
+          <t>80046</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19612; 41821</t>
+          <t>20426; 42442</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11691; 33180</t>
+          <t>12722; 32720</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16866; 37932</t>
+          <t>17406; 36237</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5261; 23092</t>
+          <t>9559; 24699</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>42147; 71657</t>
+          <t>41917; 72665</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41003; 72133</t>
+          <t>41409; 68990</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55842; 90263</t>
+          <t>57047; 92327</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>45835; 69000</t>
+          <t>51712; 78911</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66197; 105297</t>
+          <t>67626; 105411</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>57341; 92989</t>
+          <t>57937; 94537</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>78593; 121342</t>
+          <t>78933; 119325</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>41163; 86952</t>
+          <t>66500; 96773</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111757</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>262196</t>
+          <t>286257</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>373953</t>
+          <t>408011</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>55132; 88484</t>
+          <t>54910; 87621</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>86537; 132995</t>
+          <t>86262; 133819</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>58629; 92928</t>
+          <t>58476; 94031</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85505; 134337</t>
+          <t>100742; 146123</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>190996; 247695</t>
+          <t>190667; 247809</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>264554; 331394</t>
+          <t>262954; 334706</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>220920; 288598</t>
+          <t>223117; 286399</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>214142; 293572</t>
+          <t>259442; 312595</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>259067; 319516</t>
+          <t>256746; 323336</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>364473; 448511</t>
+          <t>362663; 444459</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>294186; 365908</t>
+          <t>294586; 366535</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>323773; 413007</t>
+          <t>375286; 444858</t>
         </is>
       </c>
     </row>
